--- a/exercise/Admin/Admin Ekspedisi/Tes Excel Admin Ekspedisi 1.xlsx
+++ b/exercise/Admin/Admin Ekspedisi/Tes Excel Admin Ekspedisi 1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Ekspedisi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B53FEA-6EB5-4938-A130-E7257E29A2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
@@ -117,7 +116,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="General\ &quot;Km&quot;"/>
@@ -677,7 +676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B88673E-CF33-442E-9CEE-2786E5DD9AB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -685,19 +684,19 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" s="4" customFormat="1" ht="37.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" s="4" customFormat="1" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -905,7 +904,7 @@
       <c r="H12" s="22"/>
       <c r="I12" s="22"/>
     </row>
-    <row r="13" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9" ht="20.25" x14ac:dyDescent="0.35">
       <c r="B13" s="22" t="s">
         <v>25</v>
       </c>
@@ -967,7 +966,7 @@
     <mergeCell ref="E10:G10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E10" r:id="rId1" xr:uid="{E112174A-A4C3-4B77-BA6E-4F3694F04F5F}"/>
+    <hyperlink ref="E10" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Ekspedisi/Tes Excel Admin Ekspedisi 1.xlsx
+++ b/exercise/Admin/Admin Ekspedisi/Tes Excel Admin Ekspedisi 1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Ekspedisi\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DBF2C6-0E79-40AC-A4BD-1BAFA8B9EA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
@@ -19,10 +20,41 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
@@ -116,7 +148,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="General\ &quot;Km&quot;"/>
@@ -361,9 +393,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -384,6 +413,9 @@
     </xf>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -676,7 +708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B88673E-CF33-442E-9CEE-2786E5DD9AB6}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -684,19 +716,19 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.7109375" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" s="4" customFormat="1" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" s="4" customFormat="1" ht="37.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -735,12 +767,21 @@
       <c r="E3" s="8">
         <v>5500000</v>
       </c>
-      <c r="F3" s="17"/>
+      <c r="F3" s="17" cm="1">
+        <f t="array" ref="F3">_xlfn.IFS(D3="Lemari",10%,D3="Meja",15%,D3="Kursi",12%,D3="Dipan",8%)</f>
+        <v>0.1</v>
+      </c>
       <c r="G3" s="16">
         <v>11</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="19"/>
+      <c r="H3" s="18" cm="1">
+        <f t="array" ref="H3">_xlfn.IFS(G3&lt;5,0,G3=5,0,G3&gt;5,G3*10000)</f>
+        <v>110000</v>
+      </c>
+      <c r="I3" s="26">
+        <f>E3-(E3*F3)+H3</f>
+        <v>5060000</v>
+      </c>
     </row>
     <row r="4" spans="2:9" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="5">
@@ -755,12 +796,21 @@
       <c r="E4" s="8">
         <v>1200000</v>
       </c>
-      <c r="F4" s="17"/>
+      <c r="F4" s="17" cm="1">
+        <f t="array" ref="F4">_xlfn.IFS(D4="Lemari",10%,D4="Meja",15%,D4="Kursi",12%,D4="Dipan",8%)</f>
+        <v>0.15</v>
+      </c>
       <c r="G4" s="16">
         <v>5</v>
       </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="19"/>
+      <c r="H4" s="18" cm="1">
+        <f t="array" ref="H4">_xlfn.IFS(G4&lt;5,0,G4=5,0,G4&gt;5,G4*10000)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="26">
+        <f t="shared" ref="I4:I9" si="0">E4-(E4*F4)+H4</f>
+        <v>1020000</v>
+      </c>
     </row>
     <row r="5" spans="2:9" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="5">
@@ -775,12 +825,21 @@
       <c r="E5" s="8">
         <v>6200000</v>
       </c>
-      <c r="F5" s="17"/>
+      <c r="F5" s="17" cm="1">
+        <f t="array" ref="F5">_xlfn.IFS(D5="Lemari",10%,D5="Meja",15%,D5="Kursi",12%,D5="Dipan",8%)</f>
+        <v>0.12</v>
+      </c>
       <c r="G5" s="16">
         <v>3</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19"/>
+      <c r="H5" s="18" cm="1">
+        <f t="array" ref="H5">_xlfn.IFS(G5&lt;5,0,G5=5,0,G5&gt;5,G5*10000)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="26">
+        <f t="shared" si="0"/>
+        <v>5456000</v>
+      </c>
     </row>
     <row r="6" spans="2:9" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="5">
@@ -795,12 +854,21 @@
       <c r="E6" s="8">
         <v>3000000</v>
       </c>
-      <c r="F6" s="17"/>
+      <c r="F6" s="17" cm="1">
+        <f t="array" ref="F6">_xlfn.IFS(D6="Lemari",10%,D6="Meja",15%,D6="Kursi",12%,D6="Dipan",8%)</f>
+        <v>0.08</v>
+      </c>
       <c r="G6" s="16">
         <v>12</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
+      <c r="H6" s="18" cm="1">
+        <f t="array" ref="H6">_xlfn.IFS(G6&lt;5,0,G6=5,0,G6&gt;5,G6*10000)</f>
+        <v>120000</v>
+      </c>
+      <c r="I6" s="26">
+        <f t="shared" si="0"/>
+        <v>2880000</v>
+      </c>
     </row>
     <row r="7" spans="2:9" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="5">
@@ -815,12 +883,21 @@
       <c r="E7" s="8">
         <v>1600000</v>
       </c>
-      <c r="F7" s="17"/>
+      <c r="F7" s="17" cm="1">
+        <f t="array" ref="F7">_xlfn.IFS(D7="Lemari",10%,D7="Meja",15%,D7="Kursi",12%,D7="Dipan",8%)</f>
+        <v>0.08</v>
+      </c>
       <c r="G7" s="16">
         <v>15</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="19"/>
+      <c r="H7" s="18" cm="1">
+        <f t="array" ref="H7">_xlfn.IFS(G7&lt;5,0,G7=5,0,G7&gt;5,G7*10000)</f>
+        <v>150000</v>
+      </c>
+      <c r="I7" s="26">
+        <f t="shared" si="0"/>
+        <v>1622000</v>
+      </c>
     </row>
     <row r="8" spans="2:9" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="5">
@@ -835,12 +912,21 @@
       <c r="E8" s="8">
         <v>1800000</v>
       </c>
-      <c r="F8" s="17"/>
+      <c r="F8" s="17" cm="1">
+        <f t="array" ref="F8">_xlfn.IFS(D8="Lemari",10%,D8="Meja",15%,D8="Kursi",12%,D8="Dipan",8%)</f>
+        <v>0.1</v>
+      </c>
       <c r="G8" s="16">
         <v>8</v>
       </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
+      <c r="H8" s="18" cm="1">
+        <f t="array" ref="H8">_xlfn.IFS(G8&lt;5,0,G8=5,0,G8&gt;5,G8*10000)</f>
+        <v>80000</v>
+      </c>
+      <c r="I8" s="26">
+        <f t="shared" si="0"/>
+        <v>1700000</v>
+      </c>
     </row>
     <row r="9" spans="2:9" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="5">
@@ -855,88 +941,97 @@
       <c r="E9" s="8">
         <v>2100000</v>
       </c>
-      <c r="F9" s="17"/>
+      <c r="F9" s="17" cm="1">
+        <f t="array" ref="F9">_xlfn.IFS(D9="Lemari",10%,D9="Meja",15%,D9="Kursi",12%,D9="Dipan",8%)</f>
+        <v>0.1</v>
+      </c>
       <c r="G9" s="16">
         <v>7</v>
       </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
+      <c r="H9" s="18" cm="1">
+        <f t="array" ref="H9">_xlfn.IFS(G9&lt;5,0,G9=5,0,G9&gt;5,G9*10000)</f>
+        <v>70000</v>
+      </c>
+      <c r="I9" s="26">
+        <f t="shared" si="0"/>
+        <v>1960000</v>
+      </c>
     </row>
     <row r="10" spans="2:9" ht="26.25" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="25" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
     <row r="11" spans="2:9" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23" t="s">
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" spans="2:9" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22" t="s">
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-    </row>
-    <row r="13" spans="2:9" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="B13" s="22" t="s">
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+    </row>
+    <row r="13" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="24" t="s">
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="2:9" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
     </row>
     <row r="15" spans="2:9" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
       <c r="F15" s="10"/>
       <c r="G15" s="9"/>
       <c r="H15" s="10"/>
@@ -966,7 +1061,7 @@
     <mergeCell ref="E10:G10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E10" r:id="rId1"/>
+    <hyperlink ref="E10" r:id="rId1" xr:uid="{E112174A-A4C3-4B77-BA6E-4F3694F04F5F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
